--- a/src/Features/Integration/data/2025_sem2/fr/1.xlsx
+++ b/src/Features/Integration/data/2025_sem2/fr/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\coding\ScheduleLib\src\Features\Integration\data\2025_sem2\fr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{510D71C1-4DD3-4C96-9B20-2CEE0845276E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C97CC84C-A551-4D08-9D44-B531C9B1464B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="348" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -507,18 +507,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -529,8 +517,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -787,10 +787,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="36"/>
+      <c r="B1" s="30"/>
       <c r="C1" s="1"/>
       <c r="D1" s="2"/>
       <c r="E1" s="3"/>
@@ -806,40 +806,40 @@
       <c r="O1" s="3"/>
     </row>
     <row r="2" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="37" t="str">
+      <c r="A2" s="31" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("importrange(""1ewYDzqm5MGhpTIV9iBLWtS6m1ra_VBgBZJBlVyPX4bI"",""semI,II!a2:o135"")"),"")</f>
         <v/>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="32" t="str">
+      <c r="B2" s="32"/>
+      <c r="C2" s="35" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Anul I")</f>
         <v>Anul I</v>
       </c>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="32" t="str">
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="35" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Anul II")</f>
         <v>Anul II</v>
       </c>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="42" t="str">
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="37"/>
+      <c r="L2" s="38" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Anul III")</f>
         <v>Anul III</v>
       </c>
-      <c r="M2" s="33"/>
-      <c r="N2" s="32" t="str">
+      <c r="M2" s="37"/>
+      <c r="N2" s="35" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Anul IV")</f>
         <v>Anul IV</v>
       </c>
-      <c r="O2" s="33"/>
+      <c r="O2" s="37"/>
     </row>
     <row r="3" spans="1:15" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="39"/>
-      <c r="B3" s="40"/>
+      <c r="A3" s="33"/>
+      <c r="B3" s="34"/>
       <c r="C3" s="4" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MFR2501")</f>
         <v>MFR2501</v>
@@ -950,7 +950,7 @@
       </c>
     </row>
     <row r="5" spans="1:15" ht="66.599999999999994" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="34" t="str">
+      <c r="A5" s="39" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Luni,
 24.11.2025")</f>
         <v>Luni,
@@ -1008,7 +1008,7 @@
       <c r="O5" s="14"/>
     </row>
     <row r="6" spans="1:15" ht="66" x14ac:dyDescent="0.25">
-      <c r="A6" s="30"/>
+      <c r="A6" s="40"/>
       <c r="B6" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," II
 16:45-18:15")</f>
@@ -1097,7 +1097,7 @@
       </c>
     </row>
     <row r="7" spans="1:15" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A7" s="31"/>
+      <c r="A7" s="41"/>
       <c r="B7" s="15" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"III
 18:30-20:00")</f>
@@ -1182,7 +1182,7 @@
       </c>
     </row>
     <row r="8" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A8" s="29" t="str">
+      <c r="A8" s="42" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Marți,
 25.11.2025")</f>
         <v>Marți,
@@ -1210,7 +1210,7 @@
       <c r="O8" s="22"/>
     </row>
     <row r="9" spans="1:15" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A9" s="30"/>
+      <c r="A9" s="40"/>
       <c r="B9" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," I
 15:00-16:30")</f>
@@ -1280,7 +1280,7 @@
       <c r="O9" s="14"/>
     </row>
     <row r="10" spans="1:15" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A10" s="30"/>
+      <c r="A10" s="40"/>
       <c r="B10" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"II
 16:45-18:15")</f>
@@ -1363,7 +1363,7 @@
       </c>
     </row>
     <row r="11" spans="1:15" ht="66" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
+      <c r="A11" s="41"/>
       <c r="B11" s="15" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," III
 18:30-20:00")</f>
@@ -1447,7 +1447,7 @@
       </c>
     </row>
     <row r="12" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A12" s="29" t="str">
+      <c r="A12" s="42" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Miercuri,
 26.11.2025")</f>
         <v>Miercuri,
@@ -1475,7 +1475,7 @@
       <c r="O12" s="22"/>
     </row>
     <row r="13" spans="1:15" ht="79.2" x14ac:dyDescent="0.25">
-      <c r="A13" s="30"/>
+      <c r="A13" s="40"/>
       <c r="B13" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," I
 15:00-16:30")</f>
@@ -1544,7 +1544,7 @@
       <c r="O13" s="14"/>
     </row>
     <row r="14" spans="1:15" ht="66" x14ac:dyDescent="0.25">
-      <c r="A14" s="30"/>
+      <c r="A14" s="40"/>
       <c r="B14" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," II
 16:45-18:15")</f>
@@ -1628,7 +1628,7 @@
       </c>
     </row>
     <row r="15" spans="1:15" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="A15" s="31"/>
+      <c r="A15" s="41"/>
       <c r="B15" s="15" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"III
  18:30-20:00")</f>
@@ -1712,7 +1712,7 @@
       </c>
     </row>
     <row r="16" spans="1:15" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A16" s="29" t="str">
+      <c r="A16" s="42" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Joi,
 27.11.2025")</f>
         <v>Joi,
@@ -1745,7 +1745,7 @@
       <c r="O16" s="22"/>
     </row>
     <row r="17" spans="1:15" ht="66" x14ac:dyDescent="0.25">
-      <c r="A17" s="30"/>
+      <c r="A17" s="40"/>
       <c r="B17" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," I
 15:00-16:30")</f>
@@ -1819,7 +1819,7 @@
       <c r="O17" s="14"/>
     </row>
     <row r="18" spans="1:15" ht="66" x14ac:dyDescent="0.25">
-      <c r="A18" s="30"/>
+      <c r="A18" s="40"/>
       <c r="B18" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"II
  16:45-18:15")</f>
@@ -1908,7 +1908,7 @@
       </c>
     </row>
     <row r="19" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A19" s="31"/>
+      <c r="A19" s="41"/>
       <c r="B19" s="15" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"III
  18:30-20:00")</f>
@@ -1988,7 +1988,7 @@
       </c>
     </row>
     <row r="20" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A20" s="29" t="str">
+      <c r="A20" s="42" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Vineri,
 28.11.2025")</f>
         <v>Vineri,
@@ -2016,7 +2016,7 @@
       <c r="O20" s="22"/>
     </row>
     <row r="21" spans="1:15" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="A21" s="30"/>
+      <c r="A21" s="40"/>
       <c r="B21" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," I
 15:00-16:30")</f>
@@ -2076,7 +2076,7 @@
       <c r="O21" s="14"/>
     </row>
     <row r="22" spans="1:15" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="A22" s="30"/>
+      <c r="A22" s="40"/>
       <c r="B22" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"II
  16:45-18:15")</f>
@@ -2165,7 +2165,7 @@
       </c>
     </row>
     <row r="23" spans="1:15" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="A23" s="31"/>
+      <c r="A23" s="41"/>
       <c r="B23" s="15" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"III
  18:30-20:00")</f>
@@ -2249,7 +2249,7 @@
       </c>
     </row>
     <row r="24" spans="1:15" ht="66" x14ac:dyDescent="0.25">
-      <c r="A24" s="29" t="str">
+      <c r="A24" s="42" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Sîmbătă,
 29.11.2025")</f>
         <v>Sîmbătă,
@@ -2303,7 +2303,7 @@
       <c r="O24" s="22"/>
     </row>
     <row r="25" spans="1:15" ht="66" x14ac:dyDescent="0.25">
-      <c r="A25" s="30"/>
+      <c r="A25" s="40"/>
       <c r="B25" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"II
  09:45-11:15")</f>
@@ -2372,7 +2372,7 @@
       </c>
     </row>
     <row r="26" spans="1:15" ht="79.2" x14ac:dyDescent="0.25">
-      <c r="A26" s="30"/>
+      <c r="A26" s="40"/>
       <c r="B26" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"III
  11:30-13:00")</f>
@@ -2446,7 +2446,7 @@
       </c>
     </row>
     <row r="27" spans="1:15" ht="79.2" x14ac:dyDescent="0.25">
-      <c r="A27" s="30"/>
+      <c r="A27" s="40"/>
       <c r="B27" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IV
  13:15-14:45")</f>
@@ -2516,7 +2516,7 @@
       </c>
     </row>
     <row r="28" spans="1:15" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A28" s="30"/>
+      <c r="A28" s="40"/>
       <c r="B28" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," V
 15:00-16:30")</f>
@@ -2564,7 +2564,7 @@
       </c>
     </row>
     <row r="29" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A29" s="31"/>
+      <c r="A29" s="41"/>
       <c r="B29" s="15" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VI
  16:45-18:15")</f>
@@ -2596,7 +2596,7 @@
       <c r="O29" s="18"/>
     </row>
     <row r="30" spans="1:15" ht="79.2" x14ac:dyDescent="0.25">
-      <c r="A30" s="29" t="str">
+      <c r="A30" s="42" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Duminică,
 30.11.2025")</f>
         <v>Duminică,
@@ -2640,7 +2640,7 @@
       <c r="O30" s="22"/>
     </row>
     <row r="31" spans="1:15" ht="79.2" x14ac:dyDescent="0.25">
-      <c r="A31" s="30"/>
+      <c r="A31" s="40"/>
       <c r="B31" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"II
  09:45-11:15")</f>
@@ -2710,7 +2710,7 @@
       </c>
     </row>
     <row r="32" spans="1:15" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="A32" s="30"/>
+      <c r="A32" s="40"/>
       <c r="B32" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"III
  11:30-13:00")</f>
@@ -2793,7 +2793,7 @@
       </c>
     </row>
     <row r="33" spans="1:15" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="A33" s="30"/>
+      <c r="A33" s="40"/>
       <c r="B33" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IV
  13:15-14:45")</f>
@@ -2863,7 +2863,7 @@
       </c>
     </row>
     <row r="34" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A34" s="30"/>
+      <c r="A34" s="40"/>
       <c r="B34" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," V
 15:00-16:30")</f>
@@ -2903,7 +2903,7 @@
       </c>
     </row>
     <row r="35" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A35" s="30"/>
+      <c r="A35" s="40"/>
       <c r="B35" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VI
  16:45-18:15")</f>
@@ -2930,7 +2930,7 @@
       <c r="O35" s="14"/>
     </row>
     <row r="36" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A36" s="29" t="str">
+      <c r="A36" s="42" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Luni,
 01.12.2025")</f>
         <v>Luni,
@@ -2972,7 +2972,7 @@
       <c r="O36" s="22"/>
     </row>
     <row r="37" spans="1:15" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="A37" s="30"/>
+      <c r="A37" s="40"/>
       <c r="B37" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," II
 16:45-18:15")</f>
@@ -3016,7 +3016,7 @@
       <c r="O37" s="14"/>
     </row>
     <row r="38" spans="1:15" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="A38" s="31"/>
+      <c r="A38" s="41"/>
       <c r="B38" s="15" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"III
 18:30-20:00")</f>
@@ -3063,7 +3063,7 @@
       <c r="O38" s="18"/>
     </row>
     <row r="39" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A39" s="29" t="str">
+      <c r="A39" s="42" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Marți,
 02.12.2025")</f>
         <v>Marți,
@@ -3088,7 +3088,7 @@
       <c r="O39" s="22"/>
     </row>
     <row r="40" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A40" s="30"/>
+      <c r="A40" s="40"/>
       <c r="B40" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," I
 15:00-16:30")</f>
@@ -3118,7 +3118,7 @@
       <c r="O40" s="14"/>
     </row>
     <row r="41" spans="1:15" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A41" s="30"/>
+      <c r="A41" s="40"/>
       <c r="B41" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"II
 16:45-18:15")</f>
@@ -3188,7 +3188,7 @@
       </c>
     </row>
     <row r="42" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A42" s="31"/>
+      <c r="A42" s="41"/>
       <c r="B42" s="15" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," III
 18:30-20:00")</f>
@@ -3230,7 +3230,7 @@
       <c r="O42" s="18"/>
     </row>
     <row r="43" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A43" s="29" t="str">
+      <c r="A43" s="42" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Miercuri,
 03.12.2025")</f>
         <v>Miercuri,
@@ -3255,7 +3255,7 @@
       <c r="O43" s="22"/>
     </row>
     <row r="44" spans="1:15" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A44" s="30"/>
+      <c r="A44" s="40"/>
       <c r="B44" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," I
 15:00-16:30")</f>
@@ -3285,7 +3285,7 @@
       <c r="O44" s="14"/>
     </row>
     <row r="45" spans="1:15" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A45" s="30"/>
+      <c r="A45" s="40"/>
       <c r="B45" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," II
 16:45-18:15")</f>
@@ -3365,7 +3365,7 @@
       </c>
     </row>
     <row r="46" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A46" s="31"/>
+      <c r="A46" s="41"/>
       <c r="B46" s="15" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"III
  18:30-20:00")</f>
@@ -3387,7 +3387,7 @@
       <c r="O46" s="18"/>
     </row>
     <row r="47" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="29" t="str">
+      <c r="A47" s="42" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Joi,
 04.12.2025")</f>
         <v>Joi,
@@ -3412,7 +3412,7 @@
       <c r="O47" s="22"/>
     </row>
     <row r="48" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A48" s="30"/>
+      <c r="A48" s="40"/>
       <c r="B48" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," I
 15:00-16:30")</f>
@@ -3434,7 +3434,7 @@
       <c r="O48" s="14"/>
     </row>
     <row r="49" spans="1:15" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A49" s="30"/>
+      <c r="A49" s="40"/>
       <c r="B49" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"II
  16:45-18:15")</f>
@@ -3516,7 +3516,7 @@
       </c>
     </row>
     <row r="50" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A50" s="31"/>
+      <c r="A50" s="41"/>
       <c r="B50" s="15" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"III
  18:30-20:00")</f>
@@ -3538,7 +3538,7 @@
       <c r="O50" s="18"/>
     </row>
     <row r="51" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A51" s="29" t="str">
+      <c r="A51" s="42" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Vineri,
 05.12.2025")</f>
         <v>Vineri,
@@ -3563,7 +3563,7 @@
       <c r="O51" s="22"/>
     </row>
     <row r="52" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A52" s="30"/>
+      <c r="A52" s="40"/>
       <c r="B52" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," I
 15:00-16:30")</f>
@@ -3595,7 +3595,7 @@
       <c r="O52" s="14"/>
     </row>
     <row r="53" spans="1:15" ht="105.6" x14ac:dyDescent="0.25">
-      <c r="A53" s="30"/>
+      <c r="A53" s="40"/>
       <c r="B53" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"II
  16:45-18:15")</f>
@@ -3672,7 +3672,7 @@
       </c>
     </row>
     <row r="54" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A54" s="31"/>
+      <c r="A54" s="41"/>
       <c r="B54" s="15" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"III
  18:30-20:00")</f>
@@ -3694,7 +3694,7 @@
       <c r="O54" s="18"/>
     </row>
     <row r="55" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A55" s="29" t="str">
+      <c r="A55" s="42" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Sîmbătă,
 06.12.2025")</f>
         <v>Sîmbătă,
@@ -3721,7 +3721,7 @@
       <c r="O55" s="22"/>
     </row>
     <row r="56" spans="1:15" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A56" s="30"/>
+      <c r="A56" s="40"/>
       <c r="B56" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"II
  09:45-11:15")</f>
@@ -3776,7 +3776,7 @@
       </c>
     </row>
     <row r="57" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A57" s="30"/>
+      <c r="A57" s="40"/>
       <c r="B57" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"III
  11:30-13:00")</f>
@@ -3803,7 +3803,7 @@
       <c r="O57" s="14"/>
     </row>
     <row r="58" spans="1:15" ht="66" x14ac:dyDescent="0.25">
-      <c r="A58" s="30"/>
+      <c r="A58" s="40"/>
       <c r="B58" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IV
  13:15-14:45")</f>
@@ -3838,7 +3838,7 @@
       <c r="O58" s="14"/>
     </row>
     <row r="59" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A59" s="30"/>
+      <c r="A59" s="40"/>
       <c r="B59" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," V
 15:00-16:30")</f>
@@ -3865,7 +3865,7 @@
       <c r="O59" s="14"/>
     </row>
     <row r="60" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A60" s="31"/>
+      <c r="A60" s="41"/>
       <c r="B60" s="15" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VI
  16:45-18:15")</f>
@@ -3892,7 +3892,7 @@
       <c r="O60" s="18"/>
     </row>
     <row r="61" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A61" s="29" t="str">
+      <c r="A61" s="42" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Duminică,
 07.12.2025")</f>
         <v>Duminică,
@@ -3919,7 +3919,7 @@
       <c r="O61" s="22"/>
     </row>
     <row r="62" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A62" s="30"/>
+      <c r="A62" s="40"/>
       <c r="B62" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"II
  09:45-11:15")</f>
@@ -3956,7 +3956,7 @@
       <c r="O62" s="14"/>
     </row>
     <row r="63" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A63" s="30"/>
+      <c r="A63" s="40"/>
       <c r="B63" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"III
  11:30-13:00")</f>
@@ -3983,7 +3983,7 @@
       <c r="O63" s="14"/>
     </row>
     <row r="64" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A64" s="30"/>
+      <c r="A64" s="40"/>
       <c r="B64" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IV
  13:15-14:45")</f>
@@ -4005,7 +4005,7 @@
       <c r="O64" s="14"/>
     </row>
     <row r="65" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A65" s="30"/>
+      <c r="A65" s="40"/>
       <c r="B65" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," V
 15:00-16:30")</f>
@@ -4027,7 +4027,7 @@
       <c r="O65" s="14"/>
     </row>
     <row r="66" spans="1:15" ht="27" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="30"/>
+      <c r="A66" s="40"/>
       <c r="B66" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VI
  16:45-18:15")</f>
@@ -4049,7 +4049,7 @@
       <c r="O66" s="14"/>
     </row>
     <row r="67" spans="1:15" ht="27" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="29" t="str">
+      <c r="A67" s="42" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Luni,
 08.12.2025")</f>
         <v>Luni,
@@ -4076,7 +4076,7 @@
       <c r="O67" s="22"/>
     </row>
     <row r="68" spans="1:15" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A68" s="30"/>
+      <c r="A68" s="40"/>
       <c r="B68" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," II
 16:45-18:15")</f>
@@ -4154,7 +4154,7 @@
       <c r="O68" s="14"/>
     </row>
     <row r="69" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A69" s="31"/>
+      <c r="A69" s="41"/>
       <c r="B69" s="15" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"III
 18:30-20:00")</f>
@@ -4224,7 +4224,7 @@
       <c r="O69" s="18"/>
     </row>
     <row r="70" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A70" s="29" t="str">
+      <c r="A70" s="42" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Marți,
 09.12.2025")</f>
         <v>Marți,
@@ -4260,7 +4260,7 @@
       <c r="O70" s="22"/>
     </row>
     <row r="71" spans="1:15" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A71" s="30"/>
+      <c r="A71" s="40"/>
       <c r="B71" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"II
 16:45-18:15")</f>
@@ -4334,7 +4334,7 @@
       </c>
     </row>
     <row r="72" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A72" s="31"/>
+      <c r="A72" s="41"/>
       <c r="B72" s="15" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," III
 18:30-20:00")</f>
@@ -4396,7 +4396,7 @@
       </c>
     </row>
     <row r="73" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A73" s="29" t="str">
+      <c r="A73" s="42" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Miercuri,
 10.12.2025")</f>
         <v>Miercuri,
@@ -4426,7 +4426,7 @@
       <c r="O73" s="22"/>
     </row>
     <row r="74" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A74" s="30"/>
+      <c r="A74" s="40"/>
       <c r="B74" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," II
 16:45-18:15")</f>
@@ -4496,7 +4496,7 @@
       <c r="O74" s="14"/>
     </row>
     <row r="75" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A75" s="31"/>
+      <c r="A75" s="41"/>
       <c r="B75" s="15" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"III
  18:30-20:00")</f>
@@ -4566,7 +4566,7 @@
       <c r="O75" s="18"/>
     </row>
     <row r="76" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A76" s="29" t="str">
+      <c r="A76" s="42" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Joi,
 11.12.2025")</f>
         <v>Joi,
@@ -4591,7 +4591,7 @@
       <c r="O76" s="22"/>
     </row>
     <row r="77" spans="1:15" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A77" s="30"/>
+      <c r="A77" s="40"/>
       <c r="B77" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," I
 15:00-16:30")</f>
@@ -4621,7 +4621,7 @@
       <c r="O77" s="14"/>
     </row>
     <row r="78" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A78" s="30"/>
+      <c r="A78" s="40"/>
       <c r="B78" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"II
  16:45-18:15")</f>
@@ -4701,7 +4701,7 @@
       </c>
     </row>
     <row r="79" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A79" s="31"/>
+      <c r="A79" s="41"/>
       <c r="B79" s="15" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"III
  18:30-20:00")</f>
@@ -4781,7 +4781,7 @@
       </c>
     </row>
     <row r="80" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A80" s="29" t="str">
+      <c r="A80" s="42" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Vineri,
 12.12.2025")</f>
         <v>Vineri,
@@ -4818,7 +4818,7 @@
       <c r="O80" s="22"/>
     </row>
     <row r="81" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A81" s="30"/>
+      <c r="A81" s="40"/>
       <c r="B81" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"II
  16:45-18:15")</f>
@@ -4888,7 +4888,7 @@
       </c>
     </row>
     <row r="82" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A82" s="31"/>
+      <c r="A82" s="41"/>
       <c r="B82" s="15" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"III
  18:30-20:00")</f>
@@ -4958,7 +4958,7 @@
       </c>
     </row>
     <row r="83" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A83" s="29" t="str">
+      <c r="A83" s="42" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Sîmbătă,
 13.12.2025")</f>
         <v>Sîmbătă,
@@ -4985,7 +4985,7 @@
       <c r="O83" s="22"/>
     </row>
     <row r="84" spans="1:15" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A84" s="30"/>
+      <c r="A84" s="40"/>
       <c r="B84" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"II
  09:45-11:15")</f>
@@ -5025,7 +5025,7 @@
       <c r="O84" s="14"/>
     </row>
     <row r="85" spans="1:15" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="A85" s="30"/>
+      <c r="A85" s="40"/>
       <c r="B85" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"III
  11:30-13:00")</f>
@@ -5084,7 +5084,7 @@
       <c r="O85" s="14"/>
     </row>
     <row r="86" spans="1:15" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="A86" s="30"/>
+      <c r="A86" s="40"/>
       <c r="B86" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IV
  13:15-14:45")</f>
@@ -5150,7 +5150,7 @@
       <c r="O86" s="14"/>
     </row>
     <row r="87" spans="1:15" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="A87" s="30"/>
+      <c r="A87" s="40"/>
       <c r="B87" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," V
 15:00-16:30")</f>
@@ -5221,7 +5221,7 @@
       <c r="O87" s="14"/>
     </row>
     <row r="88" spans="1:15" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="A88" s="31"/>
+      <c r="A88" s="41"/>
       <c r="B88" s="15" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VI
  16:45-18:15")</f>
@@ -5277,7 +5277,7 @@
       <c r="O88" s="18"/>
     </row>
     <row r="89" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A89" s="29" t="str">
+      <c r="A89" s="42" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Duminică,
 14.12.2025")</f>
         <v>Duminică,
@@ -5324,7 +5324,7 @@
       <c r="O89" s="22"/>
     </row>
     <row r="90" spans="1:15" ht="66" x14ac:dyDescent="0.25">
-      <c r="A90" s="30"/>
+      <c r="A90" s="40"/>
       <c r="B90" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"II
  09:45-11:15")</f>
@@ -5393,7 +5393,7 @@
       <c r="O90" s="14"/>
     </row>
     <row r="91" spans="1:15" ht="66" x14ac:dyDescent="0.25">
-      <c r="A91" s="30"/>
+      <c r="A91" s="40"/>
       <c r="B91" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"III
  11:30-13:00")</f>
@@ -5457,7 +5457,7 @@
       <c r="O91" s="14"/>
     </row>
     <row r="92" spans="1:15" ht="66" x14ac:dyDescent="0.25">
-      <c r="A92" s="30"/>
+      <c r="A92" s="40"/>
       <c r="B92" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IV
  13:15-14:45")</f>
@@ -5517,7 +5517,7 @@
       <c r="O92" s="14"/>
     </row>
     <row r="93" spans="1:15" ht="66" x14ac:dyDescent="0.25">
-      <c r="A93" s="30"/>
+      <c r="A93" s="40"/>
       <c r="B93" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," V
 15:00-16:30")</f>
@@ -5572,7 +5572,7 @@
       <c r="O93" s="14"/>
     </row>
     <row r="94" spans="1:15" ht="27" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="30"/>
+      <c r="A94" s="40"/>
       <c r="B94" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VI
  16:45-18:15")</f>
@@ -5604,7 +5604,7 @@
       <c r="O94" s="14"/>
     </row>
     <row r="95" spans="1:15" ht="27" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="29" t="str">
+      <c r="A95" s="42" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Luni,
 15.12.2025")</f>
         <v>Luni,
@@ -5651,7 +5651,7 @@
       <c r="O95" s="22"/>
     </row>
     <row r="96" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A96" s="30"/>
+      <c r="A96" s="40"/>
       <c r="B96" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," II
 16:45-18:15")</f>
@@ -5724,7 +5724,7 @@
       <c r="O96" s="14"/>
     </row>
     <row r="97" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A97" s="31"/>
+      <c r="A97" s="41"/>
       <c r="B97" s="15" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"III
 18:30-20:00")</f>
@@ -5792,7 +5792,7 @@
       <c r="O97" s="18"/>
     </row>
     <row r="98" spans="1:15" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A98" s="29" t="str">
+      <c r="A98" s="42" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Marți,
 16.12.2025")</f>
         <v>Marți,
@@ -5844,7 +5844,7 @@
       <c r="O98" s="22"/>
     </row>
     <row r="99" spans="1:15" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A99" s="30"/>
+      <c r="A99" s="40"/>
       <c r="B99" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"II
 16:45-18:15")</f>
@@ -5916,7 +5916,7 @@
       </c>
     </row>
     <row r="100" spans="1:15" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A100" s="31"/>
+      <c r="A100" s="41"/>
       <c r="B100" s="15" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," III
 18:30-20:00")</f>
@@ -5988,7 +5988,7 @@
       </c>
     </row>
     <row r="101" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A101" s="29" t="str">
+      <c r="A101" s="42" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Miercuri,
 17.12.2025")</f>
         <v>Miercuri,
@@ -6020,7 +6020,7 @@
       <c r="O101" s="22"/>
     </row>
     <row r="102" spans="1:15" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A102" s="30"/>
+      <c r="A102" s="40"/>
       <c r="B102" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," II
 16:45-18:15")</f>
@@ -6080,7 +6080,7 @@
       </c>
     </row>
     <row r="103" spans="1:15" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A103" s="31"/>
+      <c r="A103" s="41"/>
       <c r="B103" s="15" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"III
  18:30-20:00")</f>
@@ -6145,7 +6145,7 @@
       <c r="O103" s="18"/>
     </row>
     <row r="104" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A104" s="29" t="str">
+      <c r="A104" s="42" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Joi,
 18.12.2025")</f>
         <v>Joi,
@@ -6170,7 +6170,7 @@
       <c r="O104" s="22"/>
     </row>
     <row r="105" spans="1:15" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A105" s="30"/>
+      <c r="A105" s="40"/>
       <c r="B105" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," I
 15:00-16:30")</f>
@@ -6212,7 +6212,7 @@
       <c r="O105" s="14"/>
     </row>
     <row r="106" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A106" s="30"/>
+      <c r="A106" s="40"/>
       <c r="B106" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"II
  16:45-18:15")</f>
@@ -6282,7 +6282,7 @@
       <c r="O106" s="14"/>
     </row>
     <row r="107" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A107" s="31"/>
+      <c r="A107" s="41"/>
       <c r="B107" s="15" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"III
  18:30-20:00")</f>
@@ -6352,7 +6352,7 @@
       <c r="O107" s="18"/>
     </row>
     <row r="108" spans="1:15" ht="66" x14ac:dyDescent="0.25">
-      <c r="A108" s="29" t="str">
+      <c r="A108" s="42" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Vineri,
 19.12.2025")</f>
         <v>Vineri,
@@ -6403,7 +6403,7 @@
       <c r="O108" s="22"/>
     </row>
     <row r="109" spans="1:15" ht="66" x14ac:dyDescent="0.25">
-      <c r="A109" s="30"/>
+      <c r="A109" s="40"/>
       <c r="B109" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"II
  16:45-18:15")</f>
@@ -6480,7 +6480,7 @@
       </c>
     </row>
     <row r="110" spans="1:15" ht="66" x14ac:dyDescent="0.25">
-      <c r="A110" s="31"/>
+      <c r="A110" s="41"/>
       <c r="B110" s="15" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"III
  18:30-20:00")</f>
@@ -6562,7 +6562,7 @@
       </c>
     </row>
     <row r="111" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A111" s="29" t="str">
+      <c r="A111" s="42" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Sîmbătă,
 20.12.2025")</f>
         <v>Sîmbătă,
@@ -6592,9 +6592,9 @@
       </c>
       <c r="I111" s="21" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Cript. sec.inf. (lab), 
-O. Cerbu, 251/4/4")</f>
+O. Cerbu, 251/4")</f>
         <v>Cript. sec.inf. (lab), 
-O. Cerbu, 251/4/4</v>
+O. Cerbu, 251/4</v>
       </c>
       <c r="J111" s="21"/>
       <c r="K111" s="22" t="str">
@@ -6609,7 +6609,7 @@
       <c r="O111" s="22"/>
     </row>
     <row r="112" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A112" s="30"/>
+      <c r="A112" s="40"/>
       <c r="B112" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"II
  09:45-11:15")</f>
@@ -6648,9 +6648,9 @@
       </c>
       <c r="J112" s="13" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Pedagogie (sem), 
-V. Clichici, 214/4/4")</f>
+V. Clichici, 214/4")</f>
         <v>Pedagogie (sem), 
-V. Clichici, 214/4/4</v>
+V. Clichici, 214/4</v>
       </c>
       <c r="K112" s="14" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GA 2D (lab), 
@@ -6669,7 +6669,7 @@
       <c r="O112" s="14"/>
     </row>
     <row r="113" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A113" s="30"/>
+      <c r="A113" s="40"/>
       <c r="B113" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"III
  11:30-13:00")</f>
@@ -6729,7 +6729,7 @@
       <c r="O113" s="14"/>
     </row>
     <row r="114" spans="1:15" ht="66" x14ac:dyDescent="0.25">
-      <c r="A114" s="30"/>
+      <c r="A114" s="40"/>
       <c r="B114" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IV
  13:15-14:45")</f>
@@ -6795,7 +6795,7 @@
       <c r="O114" s="14"/>
     </row>
     <row r="115" spans="1:15" ht="66" x14ac:dyDescent="0.25">
-      <c r="A115" s="30"/>
+      <c r="A115" s="40"/>
       <c r="B115" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," V
 15:00-16:30")</f>
@@ -6856,7 +6856,7 @@
       <c r="O115" s="14"/>
     </row>
     <row r="116" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A116" s="31"/>
+      <c r="A116" s="41"/>
       <c r="B116" s="15" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VI
  16:45-18:15")</f>
@@ -6893,7 +6893,7 @@
       <c r="O116" s="18"/>
     </row>
     <row r="117" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A117" s="29" t="str">
+      <c r="A117" s="42" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Duminică,
 21.12.2025")</f>
         <v>Duminică,
@@ -6930,7 +6930,7 @@
       <c r="O117" s="22"/>
     </row>
     <row r="118" spans="1:15" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A118" s="30"/>
+      <c r="A118" s="40"/>
       <c r="B118" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"II
  09:45-11:15")</f>
@@ -6977,7 +6977,7 @@
       <c r="O118" s="14"/>
     </row>
     <row r="119" spans="1:15" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A119" s="30"/>
+      <c r="A119" s="40"/>
       <c r="B119" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"III
  11:30-13:00")</f>
@@ -7029,7 +7029,7 @@
       <c r="O119" s="14"/>
     </row>
     <row r="120" spans="1:15" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A120" s="30"/>
+      <c r="A120" s="40"/>
       <c r="B120" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"IV
  13:15-14:45")</f>
@@ -7081,7 +7081,7 @@
       <c r="O120" s="14"/>
     </row>
     <row r="121" spans="1:15" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A121" s="30"/>
+      <c r="A121" s="40"/>
       <c r="B121" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," V
 15:00-16:30")</f>
@@ -7128,7 +7128,7 @@
       <c r="O121" s="14"/>
     </row>
     <row r="122" spans="1:15" ht="27" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="30"/>
+      <c r="A122" s="40"/>
       <c r="B122" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VI
  16:45-18:15")</f>
@@ -7165,7 +7165,7 @@
       <c r="O122" s="14"/>
     </row>
     <row r="123" spans="1:15" ht="66.599999999999994" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="29" t="str">
+      <c r="A123" s="42" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Luni,
 22.12.2025")</f>
         <v>Luni,
@@ -7226,7 +7226,7 @@
       <c r="O123" s="22"/>
     </row>
     <row r="124" spans="1:15" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A124" s="30"/>
+      <c r="A124" s="40"/>
       <c r="B124" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," II
 16:45-18:15")</f>
@@ -7294,7 +7294,7 @@
       <c r="O124" s="14"/>
     </row>
     <row r="125" spans="1:15" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A125" s="31"/>
+      <c r="A125" s="41"/>
       <c r="B125" s="15" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"III
 18:30-20:00")</f>
@@ -7352,7 +7352,7 @@
       <c r="O125" s="18"/>
     </row>
     <row r="126" spans="1:15" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A126" s="29" t="str">
+      <c r="A126" s="42" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Marți,
 23.12.2025")</f>
         <v>Marți,
@@ -7384,7 +7384,7 @@
       <c r="O126" s="22"/>
     </row>
     <row r="127" spans="1:15" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A127" s="30"/>
+      <c r="A127" s="40"/>
       <c r="B127" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"II
 16:45-18:15")</f>
@@ -7432,7 +7432,7 @@
       <c r="O127" s="14"/>
     </row>
     <row r="128" spans="1:15" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A128" s="31"/>
+      <c r="A128" s="41"/>
       <c r="B128" s="15" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," III
 18:30-20:00")</f>
@@ -7480,7 +7480,7 @@
       <c r="O128" s="18"/>
     </row>
     <row r="129" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A129" s="29" t="str">
+      <c r="A129" s="42" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Miercuri,
 24.12.2025")</f>
         <v>Miercuri,
@@ -7512,7 +7512,7 @@
       <c r="O129" s="22"/>
     </row>
     <row r="130" spans="1:15" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A130" s="30"/>
+      <c r="A130" s="40"/>
       <c r="B130" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," II
 16:45-18:15")</f>
@@ -7557,7 +7557,7 @@
       <c r="O130" s="14"/>
     </row>
     <row r="131" spans="1:15" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A131" s="31"/>
+      <c r="A131" s="41"/>
       <c r="B131" s="15" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"III
  18:30-20:00")</f>
@@ -7615,31 +7615,6 @@
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B3"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="A24:A29"/>
-    <mergeCell ref="A30:A35"/>
-    <mergeCell ref="A36:A38"/>
-    <mergeCell ref="A39:A42"/>
-    <mergeCell ref="A43:A46"/>
-    <mergeCell ref="A47:A50"/>
-    <mergeCell ref="A51:A54"/>
-    <mergeCell ref="A55:A60"/>
-    <mergeCell ref="A61:A66"/>
-    <mergeCell ref="A67:A69"/>
-    <mergeCell ref="A70:A72"/>
-    <mergeCell ref="A73:A75"/>
-    <mergeCell ref="A76:A79"/>
-    <mergeCell ref="A80:A82"/>
     <mergeCell ref="A83:A88"/>
     <mergeCell ref="A89:A94"/>
     <mergeCell ref="A95:A97"/>
@@ -7652,6 +7627,31 @@
     <mergeCell ref="A111:A116"/>
     <mergeCell ref="A117:A122"/>
     <mergeCell ref="A123:A125"/>
+    <mergeCell ref="A67:A69"/>
+    <mergeCell ref="A70:A72"/>
+    <mergeCell ref="A73:A75"/>
+    <mergeCell ref="A76:A79"/>
+    <mergeCell ref="A80:A82"/>
+    <mergeCell ref="A43:A46"/>
+    <mergeCell ref="A47:A50"/>
+    <mergeCell ref="A51:A54"/>
+    <mergeCell ref="A55:A60"/>
+    <mergeCell ref="A61:A66"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A24:A29"/>
+    <mergeCell ref="A30:A35"/>
+    <mergeCell ref="A36:A38"/>
+    <mergeCell ref="A39:A42"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B3"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="L2:M2"/>
   </mergeCells>
   <conditionalFormatting sqref="C5:O132">
     <cfRule type="expression" dxfId="2" priority="1">
